--- a/Я скорость.xlsx
+++ b/Я скорость.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14400" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="28">
   <si>
     <t>термы</t>
   </si>
@@ -117,11 +117,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;₽&quot;_-;\-* #,##0.00\ &quot;₽&quot;_-;_-* &quot;-&quot;??\ &quot;₽&quot;_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;₽&quot;_-;\-* #,##0\ &quot;₽&quot;_-;_-* &quot;-&quot;\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="#?/?"/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -726,8 +727,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1361,7 +1365,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N47"/>
+  <dimension ref="A1:AE47"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.1428571428571" customWidth="1"/>
@@ -1369,7 +1373,7 @@
     <col min="9" max="10" width="12.8571428571429"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:31">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1409,8 +1413,47 @@
       <c r="N1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="S1" t="s">
+        <v>0</v>
+      </c>
+      <c r="T1" t="s">
+        <v>1</v>
+      </c>
+      <c r="U1" t="s">
+        <v>2</v>
+      </c>
+      <c r="V1" t="s">
+        <v>3</v>
+      </c>
+      <c r="W1" t="s">
+        <v>4</v>
+      </c>
+      <c r="X1" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>6</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>9</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>10</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -1429,8 +1472,59 @@
       <c r="F2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:14">
+      <c r="S2" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <f t="shared" ref="T2:T13" si="0">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>1</v>
+      </c>
+      <c r="U2" s="1">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.5</v>
+      </c>
+      <c r="V2" s="1">
+        <f t="shared" ref="V2:AE2" si="1">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="W2" s="1">
+        <f t="shared" si="1"/>
+        <v>0.25</v>
+      </c>
+      <c r="X2" s="1">
+        <f t="shared" si="1"/>
+        <v>0.2</v>
+      </c>
+      <c r="Y2" s="1">
+        <f t="shared" si="1"/>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="Z2" s="1">
+        <f t="shared" si="1"/>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="AA2" s="1">
+        <f t="shared" si="1"/>
+        <v>0.125</v>
+      </c>
+      <c r="AB2" s="1">
+        <f t="shared" si="1"/>
+        <v>0.111111111111111</v>
+      </c>
+      <c r="AC2" s="1">
+        <f t="shared" si="1"/>
+        <v>0.111111111111111</v>
+      </c>
+      <c r="AD2" s="1">
+        <f t="shared" si="1"/>
+        <v>0.111111111111111</v>
+      </c>
+      <c r="AE2" s="1">
+        <f t="shared" si="1"/>
+        <v>0.111111111111111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31">
       <c r="B3" t="s">
         <v>15</v>
       </c>
@@ -1443,8 +1537,58 @@
       <c r="H3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="S3" t="s">
+        <v>2</v>
+      </c>
+      <c r="T3">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="U3">
+        <v>1</v>
+      </c>
+      <c r="V3" s="1">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.5</v>
+      </c>
+      <c r="W3" s="1">
+        <f t="shared" ref="W3:AE3" si="2">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="X3" s="1">
+        <f t="shared" si="2"/>
+        <v>0.25</v>
+      </c>
+      <c r="Y3" s="1">
+        <f t="shared" si="2"/>
+        <v>0.2</v>
+      </c>
+      <c r="Z3" s="1">
+        <f t="shared" si="2"/>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="AA3" s="1">
+        <f t="shared" si="2"/>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="AB3" s="1">
+        <f t="shared" si="2"/>
+        <v>0.125</v>
+      </c>
+      <c r="AC3" s="1">
+        <f t="shared" si="2"/>
+        <v>0.111111111111111</v>
+      </c>
+      <c r="AD3" s="1">
+        <f t="shared" si="2"/>
+        <v>0.111111111111111</v>
+      </c>
+      <c r="AE3" s="1">
+        <f t="shared" si="2"/>
+        <v>0.111111111111111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31">
       <c r="B4" t="s">
         <v>16</v>
       </c>
@@ -1466,8 +1610,58 @@
       <c r="N4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="S4" t="s">
+        <v>3</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="U4">
+        <f t="shared" ref="U4:U13" si="3">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>2</v>
+      </c>
+      <c r="V4">
+        <v>1</v>
+      </c>
+      <c r="W4" s="1">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.5</v>
+      </c>
+      <c r="X4" s="1">
+        <f t="shared" ref="X4:AE4" si="4">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="Y4" s="1">
+        <f t="shared" si="4"/>
+        <v>0.25</v>
+      </c>
+      <c r="Z4" s="1">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+      <c r="AA4" s="1">
+        <f t="shared" si="4"/>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="AB4" s="1">
+        <f t="shared" si="4"/>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="AC4" s="1">
+        <f t="shared" si="4"/>
+        <v>0.125</v>
+      </c>
+      <c r="AD4" s="1">
+        <f t="shared" si="4"/>
+        <v>0.111111111111111</v>
+      </c>
+      <c r="AE4" s="1">
+        <f t="shared" si="4"/>
+        <v>0.111111111111111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -1483,8 +1677,58 @@
       <c r="E5">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:14">
+      <c r="S5" t="s">
+        <v>4</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="V5">
+        <f t="shared" ref="V5:V10" si="5">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>2</v>
+      </c>
+      <c r="W5">
+        <v>1</v>
+      </c>
+      <c r="X5" s="1">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.5</v>
+      </c>
+      <c r="Y5" s="1">
+        <f t="shared" ref="Y5:AE5" si="6">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="Z5" s="1">
+        <f t="shared" si="6"/>
+        <v>0.25</v>
+      </c>
+      <c r="AA5" s="1">
+        <f t="shared" si="6"/>
+        <v>0.2</v>
+      </c>
+      <c r="AB5" s="1">
+        <f t="shared" si="6"/>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="AC5" s="1">
+        <f t="shared" si="6"/>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="AD5" s="1">
+        <f t="shared" si="6"/>
+        <v>0.125</v>
+      </c>
+      <c r="AE5" s="1">
+        <f t="shared" si="6"/>
+        <v>0.111111111111111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31">
       <c r="B6" t="s">
         <v>15</v>
       </c>
@@ -1500,8 +1744,58 @@
       <c r="I6">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:14">
+      <c r="S6" t="s">
+        <v>5</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="W6">
+        <f t="shared" ref="W6:W13" si="7">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>2</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="1">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.5</v>
+      </c>
+      <c r="Z6" s="1">
+        <f t="shared" ref="Z6:AE6" si="8">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AA6" s="1">
+        <f t="shared" si="8"/>
+        <v>0.25</v>
+      </c>
+      <c r="AB6" s="1">
+        <f t="shared" si="8"/>
+        <v>0.2</v>
+      </c>
+      <c r="AC6" s="1">
+        <f t="shared" si="8"/>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="AD6" s="1">
+        <f t="shared" si="8"/>
+        <v>0.142857142857143</v>
+      </c>
+      <c r="AE6" s="1">
+        <f t="shared" si="8"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31">
       <c r="B7" t="s">
         <v>16</v>
       </c>
@@ -1523,8 +1817,58 @@
       <c r="N7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="S7" t="s">
+        <v>6</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="W7">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="X7">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>2</v>
+      </c>
+      <c r="Y7">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="1">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.5</v>
+      </c>
+      <c r="AA7" s="1">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AB7" s="1">
+        <f t="shared" ref="AB7:AB9" si="9">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.25</v>
+      </c>
+      <c r="AC7" s="1">
+        <f t="shared" ref="AC7:AC10" si="10">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.2</v>
+      </c>
+      <c r="AD7" s="1">
+        <f t="shared" ref="AD7:AD11" si="11">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.166666666666667</v>
+      </c>
+      <c r="AE7" s="1">
+        <f t="shared" ref="AE7:AE12" si="12">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>0.142857142857143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1543,8 +1887,58 @@
       <c r="F8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="S8" t="s">
+        <v>7</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="5"/>
+        <v>5</v>
+      </c>
+      <c r="W8">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="X8">
+        <f t="shared" ref="X8:AA8" si="13">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>3</v>
+      </c>
+      <c r="Y8">
+        <f t="shared" si="13"/>
+        <v>2</v>
+      </c>
+      <c r="Z8">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="1">
+        <f t="shared" si="13"/>
+        <v>0.5</v>
+      </c>
+      <c r="AB8" s="1">
+        <f t="shared" si="9"/>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AC8" s="1">
+        <f t="shared" si="10"/>
+        <v>0.25</v>
+      </c>
+      <c r="AD8" s="1">
+        <f t="shared" si="11"/>
+        <v>0.2</v>
+      </c>
+      <c r="AE8" s="1">
+        <f t="shared" si="12"/>
+        <v>0.166666666666667</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31">
       <c r="B9" t="s">
         <v>15</v>
       </c>
@@ -1554,8 +1948,58 @@
       <c r="H9">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="S9" t="s">
+        <v>8</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="5"/>
+        <v>6</v>
+      </c>
+      <c r="W9">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="X9">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>4</v>
+      </c>
+      <c r="Y9">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>3</v>
+      </c>
+      <c r="Z9">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>2</v>
+      </c>
+      <c r="AA9">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="1">
+        <f t="shared" si="9"/>
+        <v>0.5</v>
+      </c>
+      <c r="AC9" s="1">
+        <f t="shared" si="10"/>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AD9" s="1">
+        <f t="shared" si="11"/>
+        <v>0.25</v>
+      </c>
+      <c r="AE9" s="1">
+        <f t="shared" si="12"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31">
       <c r="B10" t="s">
         <v>16</v>
       </c>
@@ -1577,8 +2021,58 @@
       <c r="N10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="S10" t="s">
+        <v>9</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="W10">
+        <f t="shared" si="7"/>
+        <v>6</v>
+      </c>
+      <c r="X10">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>5</v>
+      </c>
+      <c r="Y10">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>4</v>
+      </c>
+      <c r="Z10">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>3</v>
+      </c>
+      <c r="AA10">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>2</v>
+      </c>
+      <c r="AB10">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="1">
+        <f t="shared" si="10"/>
+        <v>0.5</v>
+      </c>
+      <c r="AD10" s="1">
+        <f t="shared" si="11"/>
+        <v>0.333333333333333</v>
+      </c>
+      <c r="AE10" s="1">
+        <f t="shared" si="12"/>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1597,8 +2091,58 @@
       <c r="F11">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:14">
+      <c r="S11" t="s">
+        <v>10</v>
+      </c>
+      <c r="T11">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="U11">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="V11">
+        <f t="shared" ref="V11:V13" si="14">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>8</v>
+      </c>
+      <c r="W11">
+        <f t="shared" si="7"/>
+        <v>7</v>
+      </c>
+      <c r="X11">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>6</v>
+      </c>
+      <c r="Y11">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>5</v>
+      </c>
+      <c r="Z11">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>4</v>
+      </c>
+      <c r="AA11">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>3</v>
+      </c>
+      <c r="AB11">
+        <f>IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>2</v>
+      </c>
+      <c r="AC11">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="1">
+        <f t="shared" si="11"/>
+        <v>0.5</v>
+      </c>
+      <c r="AE11" s="1">
+        <f t="shared" si="12"/>
+        <v>0.333333333333333</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31">
       <c r="B12" t="s">
         <v>15</v>
       </c>
@@ -1611,8 +2155,58 @@
       <c r="I12">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:14">
+      <c r="S12" t="s">
+        <v>11</v>
+      </c>
+      <c r="T12">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="U12">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="V12">
+        <f t="shared" si="14"/>
+        <v>9</v>
+      </c>
+      <c r="W12">
+        <f t="shared" si="7"/>
+        <v>8</v>
+      </c>
+      <c r="X12">
+        <f t="shared" ref="X12:AC12" si="15">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>7</v>
+      </c>
+      <c r="Y12">
+        <f t="shared" si="15"/>
+        <v>6</v>
+      </c>
+      <c r="Z12">
+        <f t="shared" si="15"/>
+        <v>5</v>
+      </c>
+      <c r="AA12">
+        <f t="shared" si="15"/>
+        <v>4</v>
+      </c>
+      <c r="AB12">
+        <f t="shared" si="15"/>
+        <v>3</v>
+      </c>
+      <c r="AC12">
+        <f t="shared" si="15"/>
+        <v>2</v>
+      </c>
+      <c r="AD12">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="1">
+        <f t="shared" si="12"/>
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31">
       <c r="B13" t="s">
         <v>16</v>
       </c>
@@ -1631,8 +2225,58 @@
       <c r="N13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="S13" t="s">
+        <v>12</v>
+      </c>
+      <c r="T13">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="U13">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="14"/>
+        <v>9</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="7"/>
+        <v>9</v>
+      </c>
+      <c r="X13">
+        <f t="shared" ref="X13:AD13" si="16">IF(ROW()-ROW($T$2)&gt;=COLUMN()-COLUMN($T$2),MIN(9,1+ROW()-ROW($T$2)-COLUMN()+COLUMN($T$2)),1/MIN(9,1+COLUMN()-COLUMN($T$2)-ROW()+ROW($T$2)))</f>
+        <v>8</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="16"/>
+        <v>7</v>
+      </c>
+      <c r="Z13">
+        <f t="shared" si="16"/>
+        <v>6</v>
+      </c>
+      <c r="AA13">
+        <f t="shared" si="16"/>
+        <v>5</v>
+      </c>
+      <c r="AB13">
+        <f t="shared" si="16"/>
+        <v>4</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="16"/>
+        <v>3</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="16"/>
+        <v>2</v>
+      </c>
+      <c r="AE13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1652,7 +2296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:31">
       <c r="B15" t="s">
         <v>15</v>
       </c>
@@ -1669,7 +2313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:31">
       <c r="B16" t="s">
         <v>16</v>
       </c>
@@ -2136,43 +2780,43 @@
         <v>12</v>
       </c>
       <c r="E42">
-        <f t="shared" ref="E42:M42" si="0">SUM(E2,E5,E8,E11,E14,E17,E20,E23,E26,E29,E32,E35)</f>
+        <f t="shared" ref="E42:N42" si="17">SUM(E2,E5,E8,E11,E14,E17,E20,E23,E26,E29,E32,E35)</f>
         <v>12</v>
       </c>
       <c r="F42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="17"/>
         <v>9</v>
       </c>
       <c r="G42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="H42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="I42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="J42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="K42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="L42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="M42">
-        <f t="shared" si="0"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="N42">
-        <f>SUM(N2,N5,N8,N11,N14,N17,N20,N23,N26,N29,N32,N35)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
@@ -2186,43 +2830,43 @@
         <v>1</v>
       </c>
       <c r="E43">
-        <f t="shared" ref="E43:N43" si="1">E42/12</f>
+        <f t="shared" ref="E43:N43" si="18">E42/12</f>
         <v>1</v>
       </c>
       <c r="F43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="18"/>
         <v>0.75</v>
       </c>
       <c r="G43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="H43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="I43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="J43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="K43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="L43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="M43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="N43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
@@ -2235,47 +2879,47 @@
         <v>0</v>
       </c>
       <c r="D44">
-        <f t="shared" ref="D44:N44" si="2">SUM(D3,D6,D9,D12,D15,D18,D21,D24,D27,D30,D33,D36)</f>
+        <f t="shared" ref="D44:N44" si="19">SUM(D3,D6,D9,D12,D15,D18,D21,D24,D27,D30,D33,D36)</f>
         <v>0</v>
       </c>
       <c r="E44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="F44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="19"/>
         <v>8</v>
       </c>
       <c r="G44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="19"/>
         <v>12</v>
       </c>
       <c r="H44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="19"/>
         <v>12</v>
       </c>
       <c r="I44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="19"/>
         <v>7</v>
       </c>
       <c r="J44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="K44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="L44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="M44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="N44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
     </row>
@@ -2285,47 +2929,47 @@
         <v>0</v>
       </c>
       <c r="D45">
-        <f t="shared" ref="D45:N45" si="3">D44/12</f>
+        <f t="shared" ref="D45:N45" si="20">D44/12</f>
         <v>0</v>
       </c>
       <c r="E45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="F45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>0.666666666666667</v>
       </c>
       <c r="G45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="H45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="I45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>0.583333333333333</v>
       </c>
       <c r="J45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="K45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="L45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="M45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="N45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
     </row>
@@ -2338,47 +2982,47 @@
         <v>0</v>
       </c>
       <c r="D46">
-        <f t="shared" ref="D46:N46" si="4">SUM(D4,D7,D10,D13,D16,D19,D22,D25,D28,D31,D34,D37)</f>
+        <f t="shared" ref="D46:N46" si="21">SUM(D4,D7,D10,D13,D16,D19,D22,D25,D28,D31,D34,D37)</f>
         <v>0</v>
       </c>
       <c r="E46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="F46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="G46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="H46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="I46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>8</v>
       </c>
       <c r="J46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="K46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="L46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="M46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
       <c r="N46">
-        <f t="shared" si="4"/>
+        <f t="shared" si="21"/>
         <v>12</v>
       </c>
     </row>
@@ -2388,47 +3032,47 @@
         <v>0</v>
       </c>
       <c r="D47">
-        <f t="shared" ref="D47:N47" si="5">D46/12</f>
+        <f t="shared" ref="D47:N47" si="22">D46/12</f>
         <v>0</v>
       </c>
       <c r="E47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="F47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="G47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="H47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
       <c r="I47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>0.666666666666667</v>
       </c>
       <c r="J47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="K47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="L47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="M47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
       <c r="N47">
-        <f t="shared" si="5"/>
+        <f t="shared" si="22"/>
         <v>1</v>
       </c>
     </row>
